--- a/docs/planning/briefs/content-sources/traveloure-content-source-index.xlsx
+++ b/docs/planning/briefs/content-sources/traveloure-content-source-index.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">'Providers (recruiting)'!$A$1:$M$18</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Sources!$A$1:$Q$34</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Sources!$A$1:$Q$35</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="771" uniqueCount="458">
   <si>
     <t xml:space="preserve">Traveloure content source index</t>
   </si>
@@ -356,6 +356,33 @@
   </si>
   <si>
     <t xml:space="preserve">Structured spine. Display inside plans next to a map only; cache &lt;= 30 days; never a public directory. Enable Places API (New) on the same project as Routes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">google_routes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Routes API (Compute Route Matrix)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://developers.google.com/maps/documentation/routes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API: routes.googleapis.com computeRouteMatrix, travelMode WALK | TRANSIT (no page)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transport.local, neighbourhood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">transport.local fares &amp; passes, last-service rules, transport.intercity.rail, lodging, activity, dining</t>
+  </si>
+  <si>
+    <t xml:space="preserve">held (GOOGLE_MAPS_API_KEY; Routes API enabled on TLoure 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">live — first Kyoto refresh 2026-09-29 (128 elements, 64 walk / 64 transit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feeds travel_time_matrix (A2). Transit durations come from operators' GTFS via Google. Cache limit is 30 days under Google's terms, which is why the refresh is monthly; do not lengthen it. Money and rules (passes, fares, last trains) come from the city transport source, not from here.</t>
   </si>
   <si>
     <t xml:space="preserve">booking_com</t>
@@ -1537,7 +1564,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1555,10 +1582,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1981,12 +2004,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
         <v>20</v>
       </c>
@@ -2017,212 +2040,212 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="D13" s="6" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="D14" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="D15" s="6" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2242,7 +2265,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q34"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="20"/>
@@ -2260,1609 +2283,1656 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="G2" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8" t="s">
+      <c r="M2" s="7"/>
+      <c r="N2" s="7"/>
+      <c r="O2" s="7"/>
+      <c r="P2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="Q2" s="6" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="I3" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="J3" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="M3" s="7"/>
+      <c r="N3" s="7"/>
+      <c r="O3" s="7"/>
+      <c r="P3" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G4" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8" t="s">
+      <c r="I4" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q3" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="Q4" s="6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q5" s="6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
+      <c r="P6" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q6" s="6" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E8" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="F8" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="G8" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q8" s="6" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q10" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q11" s="6" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F12" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G12" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K4" s="7" t="s">
+      <c r="H12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J12" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="L4" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="M4" s="8"/>
-      <c r="N4" s="8"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="8" t="s">
+      <c r="K12" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q4" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="Q12" s="6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="E13" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F13" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G13" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="I5" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="8"/>
-      <c r="O5" s="8"/>
-      <c r="P5" s="8" t="s">
+      <c r="H13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q5" s="7" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>127</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="Q13" s="6" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E14" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="H6" s="7" t="s">
+      <c r="F14" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q14" s="6" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I15" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="J15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="K15" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="J6" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K6" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="8" t="s">
+      <c r="L15" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q6" s="7" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K7" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="M7" s="8"/>
-      <c r="N7" s="8"/>
-      <c r="O7" s="8"/>
-      <c r="P7" s="8" t="s">
+      <c r="Q15" s="6" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q7" s="7" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="M8" s="8"/>
-      <c r="N8" s="8"/>
-      <c r="O8" s="8"/>
-      <c r="P8" s="8" t="s">
+      <c r="Q16" s="6" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H17" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q8" s="7" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K9" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
-      <c r="O9" s="8"/>
-      <c r="P9" s="8" t="s">
+      <c r="Q17" s="6" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="J18" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K18" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L18" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q9" s="7" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="M10" s="8"/>
-      <c r="N10" s="8"/>
-      <c r="O10" s="8"/>
-      <c r="P10" s="8" t="s">
+      <c r="Q18" s="6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>233</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="J19" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K19" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L19" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q10" s="7" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="8"/>
-      <c r="O11" s="8"/>
-      <c r="P11" s="8" t="s">
+      <c r="Q19" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>242</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="J20" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K20" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L20" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
+      <c r="O20" s="7"/>
+      <c r="P20" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q11" s="7" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J12" s="7" t="s">
+      <c r="Q20" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J21" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K21" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L21" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q21" s="6" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="6" t="s">
+        <v>250</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="J22" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="K22" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L22" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
+      <c r="P22" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q22" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J23" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K23" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M23" s="7"/>
+      <c r="N23" s="7"/>
+      <c r="O23" s="7"/>
+      <c r="P23" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q23" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J24" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K24" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L24" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M24" s="7"/>
+      <c r="N24" s="7"/>
+      <c r="O24" s="7"/>
+      <c r="P24" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q24" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J25" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K25" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L25" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M25" s="7"/>
+      <c r="N25" s="7"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q25" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J26" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K26" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L26" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q26" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G27" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="H27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I27" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J27" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K27" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L27" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M27" s="7"/>
+      <c r="N27" s="7"/>
+      <c r="O27" s="7"/>
+      <c r="P27" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q27" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>284</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J28" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K28" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L28" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M28" s="7"/>
+      <c r="N28" s="7"/>
+      <c r="O28" s="7"/>
+      <c r="P28" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q28" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="H29" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I29" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J29" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K29" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L29" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M29" s="7"/>
+      <c r="N29" s="7"/>
+      <c r="O29" s="7"/>
+      <c r="P29" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q29" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F30" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G30" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="H30" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="I30" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J30" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K30" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L30" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M30" s="7"/>
+      <c r="N30" s="7"/>
+      <c r="O30" s="7"/>
+      <c r="P30" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q30" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G31" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="H31" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="I31" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J31" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K31" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L31" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M31" s="7"/>
+      <c r="N31" s="7"/>
+      <c r="O31" s="7"/>
+      <c r="P31" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q31" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F32" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I32" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="J32" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K32" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L32" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q32" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G33" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="I33" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="J33" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="K12" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="8" t="s">
+      <c r="K33" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L33" s="6" t="s">
+        <v>310</v>
+      </c>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q12" s="7" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="M13" s="8"/>
-      <c r="N13" s="8"/>
-      <c r="O13" s="8"/>
-      <c r="P13" s="8" t="s">
+      <c r="Q33" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>314</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G34" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J34" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K34" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L34" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q13" s="7" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>194</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>196</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="K14" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>198</v>
-      </c>
-      <c r="M14" s="8"/>
-      <c r="N14" s="8"/>
-      <c r="O14" s="8"/>
-      <c r="P14" s="8" t="s">
+      <c r="Q34" s="6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J35" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="K35" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M35" s="7"/>
+      <c r="N35" s="7"/>
+      <c r="O35" s="7"/>
+      <c r="P35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="Q14" s="7" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>201</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>208</v>
-      </c>
-      <c r="J15" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="8"/>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q15" s="7" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="J16" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M16" s="8"/>
-      <c r="N16" s="8"/>
-      <c r="O16" s="8"/>
-      <c r="P16" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q16" s="7" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>220</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>221</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="J17" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M17" s="8"/>
-      <c r="N17" s="8"/>
-      <c r="O17" s="8"/>
-      <c r="P17" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q17" s="7" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>224</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>225</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>226</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="J18" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K18" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q18" s="7" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>231</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>232</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H19" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K19" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>228</v>
-      </c>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
-      <c r="P19" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q19" s="7" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G20" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H20" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J20" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M20" s="8"/>
-      <c r="N20" s="8"/>
-      <c r="O20" s="8"/>
-      <c r="P20" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q20" s="7" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
-        <v>241</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7" t="s">
-        <v>243</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="H21" s="7" t="s">
-        <v>245</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>246</v>
-      </c>
-      <c r="J21" s="7" t="s">
-        <v>244</v>
-      </c>
-      <c r="K21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="8"/>
-      <c r="P21" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q21" s="7" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>248</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>249</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>251</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>253</v>
-      </c>
-      <c r="I22" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="J22" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L22" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M22" s="8"/>
-      <c r="N22" s="8"/>
-      <c r="O22" s="8"/>
-      <c r="P22" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q22" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>256</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>257</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>259</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="H23" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I23" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K23" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L23" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q23" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>260</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>261</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F24" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="H24" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J24" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L24" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-      <c r="O24" s="8"/>
-      <c r="P24" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q24" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
+      <c r="Q35" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="H25" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I25" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="J25" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L25" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
-      <c r="P25" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q25" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
-        <v>269</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>270</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>272</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I26" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J26" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L26" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M26" s="8"/>
-      <c r="N26" s="8"/>
-      <c r="O26" s="8"/>
-      <c r="P26" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q26" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="B27" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>276</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="H27" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I27" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J27" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L27" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M27" s="8"/>
-      <c r="N27" s="8"/>
-      <c r="O27" s="8"/>
-      <c r="P27" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q27" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>277</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>278</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H28" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I28" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="J28" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L28" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M28" s="8"/>
-      <c r="N28" s="8"/>
-      <c r="O28" s="8"/>
-      <c r="P28" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q28" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="I29" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J29" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L29" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M29" s="8"/>
-      <c r="N29" s="8"/>
-      <c r="O29" s="8"/>
-      <c r="P29" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q29" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="7" t="s">
-        <v>286</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>289</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="H30" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="I30" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="J30" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L30" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M30" s="8"/>
-      <c r="N30" s="8"/>
-      <c r="O30" s="8"/>
-      <c r="P30" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q30" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>294</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G31" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="H31" s="7" t="s">
-        <v>215</v>
-      </c>
-      <c r="I31" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="J31" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L31" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M31" s="8"/>
-      <c r="N31" s="8"/>
-      <c r="O31" s="8"/>
-      <c r="P31" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q31" s="7" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="7" t="s">
-        <v>296</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>298</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>299</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F32" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="G32" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="J32" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="K32" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L32" s="7" t="s">
-        <v>301</v>
-      </c>
-      <c r="M32" s="8"/>
-      <c r="N32" s="8"/>
-      <c r="O32" s="8"/>
-      <c r="P32" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q32" s="7" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="7" t="s">
-        <v>303</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>304</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>305</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>306</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>307</v>
-      </c>
-      <c r="H33" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="I33" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="J33" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L33" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-      <c r="P33" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q33" s="7" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>314</v>
-      </c>
-      <c r="H34" s="7" t="s">
-        <v>308</v>
-      </c>
-      <c r="I34" s="7" t="s">
-        <v>254</v>
-      </c>
-      <c r="J34" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K34" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="L34" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="8"/>
-      <c r="P34" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q34" s="7" t="s">
-        <v>255</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q34"/>
+  <autoFilter ref="A1:Q35"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3891,324 +3961,324 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>318</v>
+      <c r="B1" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="7" t="str">
+      <c r="B2" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A2,Needs!$A$2:$A$15,0))</f>
         <v>yes</v>
       </c>
-      <c r="C2" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A2,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C2" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A2,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D2" s="7" t="str">
+      <c r="D2" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B2,3)="yes",C2=0),"GAP",IF(C2=0,"uncovered","ok"))</f>
         <v>GAP</v>
       </c>
-      <c r="E2" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A2,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E2" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A2,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="7" t="str">
+      <c r="B3" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A3,Needs!$A$2:$A$15,0))</f>
         <v>recommended</v>
       </c>
-      <c r="C3" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A3,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C3" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A3,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D3" s="7" t="str">
+      <c r="D3" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B3,3)="yes",C3=0),"GAP",IF(C3=0,"uncovered","ok"))</f>
         <v>uncovered</v>
       </c>
-      <c r="E3" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A3,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E3" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A3,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="7" t="str">
+      <c r="B4" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A4,Needs!$A$2:$A$15,0))</f>
         <v>recommended</v>
       </c>
-      <c r="C4" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A4,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C4" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A4,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D4" s="7" t="str">
+      <c r="D4" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B4,3)="yes",C4=0),"GAP",IF(C4=0,"uncovered","ok"))</f>
         <v>uncovered</v>
       </c>
-      <c r="E4" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A4,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E4" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A4,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>4</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A5,Needs!$A$2:$A$15,0))</f>
         <v>no</v>
       </c>
-      <c r="C5" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A5,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C5" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A5,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D5" s="7" t="str">
+      <c r="D5" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B5,3)="yes",C5=0),"GAP",IF(C5=0,"uncovered","ok"))</f>
         <v>uncovered</v>
       </c>
-      <c r="E5" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A5,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E5" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A5,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="7" t="str">
+      <c r="B6" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A6,Needs!$A$2:$A$15,0))</f>
         <v>no</v>
       </c>
-      <c r="C6" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A6,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C6" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A6,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D6" s="7" t="str">
+      <c r="D6" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B6,3)="yes",C6=0),"GAP",IF(C6=0,"uncovered","ok"))</f>
         <v>uncovered</v>
       </c>
-      <c r="E6" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A6,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E6" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A6,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A7,Needs!$A$2:$A$15,0))</f>
         <v>no</v>
       </c>
-      <c r="C7" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A7,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C7" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A7,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D7" s="7" t="str">
+      <c r="D7" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B7,3)="yes",C7=0),"GAP",IF(C7=0,"uncovered","ok"))</f>
         <v>uncovered</v>
       </c>
-      <c r="E7" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A7,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E7" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A7,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A8,Needs!$A$2:$A$15,0))</f>
         <v>yes</v>
       </c>
-      <c r="C8" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A8,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C8" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A8,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D8" s="7" t="str">
+      <c r="D8" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B8,3)="yes",C8=0),"GAP",IF(C8=0,"uncovered","ok"))</f>
         <v>GAP</v>
       </c>
-      <c r="E8" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A8,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
-        <v>2</v>
+      <c r="E8" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A8,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B9" s="7" t="str">
+      <c r="B9" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A9,Needs!$A$2:$A$15,0))</f>
         <v>yes</v>
       </c>
-      <c r="C9" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A9,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C9" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A9,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D9" s="7" t="str">
+      <c r="D9" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B9,3)="yes",C9=0),"GAP",IF(C9=0,"uncovered","ok"))</f>
         <v>GAP</v>
       </c>
-      <c r="E9" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A9,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E9" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A9,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="7" t="str">
+      <c r="B10" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A10,Needs!$A$2:$A$15,0))</f>
         <v>yes</v>
       </c>
-      <c r="C10" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A10,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C10" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A10,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D10" s="7" t="str">
+      <c r="D10" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B10,3)="yes",C10=0),"GAP",IF(C10=0,"uncovered","ok"))</f>
         <v>GAP</v>
       </c>
-      <c r="E10" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A10,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E10" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A10,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="7" t="str">
+      <c r="B11" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A11,Needs!$A$2:$A$15,0))</f>
         <v>yes</v>
       </c>
-      <c r="C11" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A11,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C11" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A11,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D11" s="7" t="str">
+      <c r="D11" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B11,3)="yes",C11=0),"GAP",IF(C11=0,"uncovered","ok"))</f>
         <v>GAP</v>
       </c>
-      <c r="E11" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A11,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E11" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A11,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="7" t="str">
+      <c r="B12" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A12,Needs!$A$2:$A$15,0))</f>
         <v>yes (platform listings first)</v>
       </c>
-      <c r="C12" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A12,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C12" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A12,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D12" s="7" t="str">
+      <c r="D12" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B12,3)="yes",C12=0),"GAP",IF(C12=0,"uncovered","ok"))</f>
         <v>GAP</v>
       </c>
-      <c r="E12" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A12,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E12" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A12,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B13" s="7" t="str">
+      <c r="B13" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A13,Needs!$A$2:$A$15,0))</f>
         <v>recommended</v>
       </c>
-      <c r="C13" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A13,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C13" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A13,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D13" s="7" t="str">
+      <c r="D13" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B13,3)="yes",C13=0),"GAP",IF(C13=0,"uncovered","ok"))</f>
         <v>uncovered</v>
       </c>
-      <c r="E13" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A13,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E13" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A13,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B14" s="7" t="str">
+      <c r="B14" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A14,Needs!$A$2:$A$15,0))</f>
         <v>recommended</v>
       </c>
-      <c r="C14" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A14,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C14" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A14,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D14" s="7" t="str">
+      <c r="D14" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B14,3)="yes",C14=0),"GAP",IF(C14=0,"uncovered","ok"))</f>
         <v>uncovered</v>
       </c>
-      <c r="E14" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A14,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
+      <c r="E14" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A14,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
         <v>3</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B15" s="7" t="str">
+      <c r="B15" s="6" t="str">
         <f aca="false">INDEX(Needs!$C$2:$C$15,MATCH(A15,Needs!$A$2:$A$15,0))</f>
         <v>yes</v>
       </c>
-      <c r="C15" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A15,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0),--(Sources!$P$2:$P$34="yes"))</f>
+      <c r="C15" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A15,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0),--(Sources!$P$2:$P$35="yes"))</f>
         <v>0</v>
       </c>
-      <c r="D15" s="7" t="str">
+      <c r="D15" s="6" t="str">
         <f aca="false">IF(AND(LEFT(B15,3)="yes",C15=0),"GAP",IF(C15=0,"uncovered","ok"))</f>
         <v>GAP</v>
       </c>
-      <c r="E15" s="7" t="n">
-        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A15,Sources!$H$2:$H$34)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$34))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$34))&gt;0))</f>
-        <v>3</v>
+      <c r="E15" s="6" t="n">
+        <f aca="false">SUMPRODUCT(--ISNUMBER(SEARCH(A15,Sources!$H$2:$H$35)),--(ISNUMBER(SEARCH("kyoto",Sources!$G$2:$G$35))+ISNUMBER(SEARCH("global",Sources!$G$2:$G$35))&gt;0))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="9" t="s">
-        <v>319</v>
-      </c>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="9"/>
+      <c r="A17" s="8" t="s">
+        <v>328</v>
+      </c>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4245,629 +4315,629 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="F1" s="6" t="s">
+      <c r="B1" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>331</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>332</v>
+      </c>
+      <c r="F1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>325</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>326</v>
-      </c>
-      <c r="J1" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="L1" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="M1" s="6" t="s">
+      <c r="G1" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>334</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="M1" s="5" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>335</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>337</v>
-      </c>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="7" t="s">
-        <v>338</v>
+      <c r="A2" s="6" t="s">
+        <v>339</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>341</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>342</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>343</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="M2" s="6" t="s">
+        <v>347</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>339</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="A3" s="6" t="s">
+        <v>348</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>340</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>343</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>344</v>
-      </c>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
-      <c r="M3" s="7"/>
+      <c r="D3" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>369</v>
+      </c>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="6" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="6"/>
+    </row>
+    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>381</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="6" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>389</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>390</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>391</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>395</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>396</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>400</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="6" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>406</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>407</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>410</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>411</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>412</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>413</v>
+      </c>
+      <c r="H11" s="6" t="s">
         <v>345</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>347</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>348</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>350</v>
-      </c>
-      <c r="H4" s="7" t="s">
+      <c r="I11" s="6" t="s">
+        <v>414</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="I4" s="7" t="s">
-        <v>352</v>
-      </c>
-      <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-      <c r="L4" s="8"/>
-      <c r="M4" s="7"/>
-    </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>353</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="G12" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>420</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>423</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>424</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>299</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>430</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>432</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>340</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>434</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>356</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="D16" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="H5" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="I5" s="7" t="s">
+      <c r="G16" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="J5" s="8"/>
-      <c r="K5" s="8"/>
-      <c r="L5" s="8"/>
-      <c r="M5" s="7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>362</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="I16" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="6" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6" t="s">
+        <v>442</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>364</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>365</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="D17" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>367</v>
-      </c>
-      <c r="H6" s="7" t="s">
+      <c r="G17" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="H17" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="I6" s="7" t="s">
-        <v>369</v>
-      </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="7"/>
-    </row>
-    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>370</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>374</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>375</v>
-      </c>
-      <c r="H7" s="7" t="s">
-        <v>376</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>377</v>
-      </c>
-      <c r="J7" s="8"/>
-      <c r="K7" s="8"/>
-      <c r="L7" s="8"/>
-      <c r="M7" s="7" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
-        <v>379</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>363</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>381</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>382</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>383</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>368</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>384</v>
-      </c>
-      <c r="J8" s="8"/>
-      <c r="K8" s="8"/>
-      <c r="L8" s="8"/>
-      <c r="M8" s="7"/>
-    </row>
-    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>385</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>386</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>387</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>388</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>390</v>
-      </c>
-      <c r="H9" s="7" t="s">
-        <v>391</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>392</v>
-      </c>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="7" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>394</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>395</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>396</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>397</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>398</v>
-      </c>
-      <c r="H10" s="7" t="s">
-        <v>399</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>400</v>
-      </c>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-      <c r="L10" s="8"/>
-      <c r="M10" s="7"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>401</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>252</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>402</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>403</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>389</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>404</v>
-      </c>
-      <c r="H11" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>405</v>
-      </c>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
-        <v>407</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>268</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>408</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>409</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>410</v>
-      </c>
-      <c r="H12" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>411</v>
-      </c>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>281</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>413</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>415</v>
-      </c>
-      <c r="H13" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>416</v>
-      </c>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="8"/>
-      <c r="M13" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
-        <v>417</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>290</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>418</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>419</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>420</v>
-      </c>
-      <c r="H14" s="7" t="s">
-        <v>421</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="J14" s="8"/>
-      <c r="K14" s="8"/>
-      <c r="L14" s="8"/>
-      <c r="M14" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>425</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>342</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>426</v>
-      </c>
-      <c r="H15" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>346</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>430</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>349</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>431</v>
-      </c>
-      <c r="H16" s="7" t="s">
-        <v>351</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>354</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>435</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>436</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>357</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="H17" s="7" t="s">
-        <v>359</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="J17" s="8"/>
-      <c r="K17" s="8"/>
-      <c r="L17" s="8"/>
-      <c r="M17" s="7" t="s">
-        <v>439</v>
+      <c r="I17" s="6" t="s">
+        <v>447</v>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="6" t="s">
+        <v>448</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
-        <v>440</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>441</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="E18" s="7" t="s">
+      <c r="A18" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>443</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="H18" s="7" t="s">
-        <v>446</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="7" t="s">
-        <v>448</v>
+      <c r="C18" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="H18" s="6" t="s">
+        <v>455</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="6" t="s">
+        <v>457</v>
       </c>
     </row>
   </sheetData>
